--- a/config/gold-and-gears-generated/templates/GoldAndGearsProgression.xlsx
+++ b/config/gold-and-gears-generated/templates/GoldAndGearsProgression.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="166">
   <si>
     <t>@table</t>
   </si>
@@ -213,7 +213,7 @@
     <t>GoldGearsNeuralNetwork</t>
   </si>
   <si>
-    <t>08bb2c15569e2843</t>
+    <t>5b3bf185c7cac3f1</t>
   </si>
   <si>
     <t>mechanism_quality</t>
@@ -288,7 +288,7 @@
     <t>GoldGearsConundrumLevel</t>
   </si>
   <si>
-    <t>114c8d100249a1be</t>
+    <t>380f5b3e223cefb0</t>
   </si>
   <si>
     <t>source_type</t>
@@ -465,7 +465,7 @@
     <t>GoldGearsResonanceExtrapolation</t>
   </si>
   <si>
-    <t>2f5703dd31a18e10</t>
+    <t>2633dcba2071f0b6</t>
   </si>
   <si>
     <t>buff_group_id</t>
@@ -1523,7 +1523,7 @@
     <col min="11" max="11" width="28.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="30.7109375" style="5" customWidth="1"/>
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="30.7109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="22.7109375" style="5" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" style="5" customWidth="1"/>
     <col min="18" max="18" width="17.7109375" style="5" customWidth="1"/>
@@ -1831,7 +1831,7 @@
         <v>46</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>42</v>
@@ -2038,7 +2038,9 @@
       <c r="N6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="5"/>
+      <c r="O6" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="P6" s="5" t="s">
         <v>84</v>
       </c>
@@ -2138,7 +2140,7 @@
       <c r="AI7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="6">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." sqref="B8:B1007">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
@@ -2150,9 +2152,6 @@
       <formula1>"DataReady"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="O8:O1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." sqref="R8:R1007">
@@ -2181,7 +2180,7 @@
     <col min="11" max="11" width="28.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="30.7109375" style="5" customWidth="1"/>
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="30.7109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="22.7109375" style="5" customWidth="1"/>
     <col min="17" max="21" width="12.7109375" style="5" customWidth="1"/>
     <col min="22" max="23" width="19.7109375" style="5" customWidth="1"/>
@@ -2488,7 +2487,7 @@
         <v>46</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>42</v>
@@ -2695,7 +2694,9 @@
       <c r="N6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="5"/>
+      <c r="O6" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="P6" s="5" t="s">
         <v>84</v>
       </c>
@@ -2797,7 +2798,7 @@
       <c r="AI7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
+  <dataValidations count="9">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 0 to 2147483647." sqref="AB8:AB1007">
       <formula1>0</formula1>
       <formula2>2147483647</formula2>
@@ -2817,9 +2818,6 @@
       <formula1>"DataReady"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="O8:O1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 6." promptTitle="Integer range" prompt="Enter an integer from 1 to 6." sqref="T8:T1007">
@@ -4397,7 +4395,7 @@
     <col min="11" max="11" width="28.7109375" style="5" customWidth="1"/>
     <col min="12" max="12" width="30.7109375" style="5" customWidth="1"/>
     <col min="13" max="14" width="22.7109375" style="5" customWidth="1"/>
-    <col min="15" max="15" width="30.7109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="5" customWidth="1"/>
     <col min="16" max="16" width="22.7109375" style="5" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" style="5" customWidth="1"/>
     <col min="18" max="18" width="21.7109375" style="5" customWidth="1"/>
@@ -4696,7 +4694,7 @@
         <v>46</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>42</v>
@@ -4891,7 +4889,9 @@
       <c r="N6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="5"/>
+      <c r="O6" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="P6" s="5" t="s">
         <v>84</v>
       </c>
@@ -4979,7 +4979,7 @@
       <c r="AG7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." sqref="B8:B1007">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
@@ -4991,9 +4991,6 @@
       <formula1>"DataReady"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
-      <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="GoldGearsEvidenceQuality enum" prompt="Select a value from the dropdown." sqref="O8:O1007">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="U8:U1007">
